--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/namamani.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/namamani.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="namamani" sheetId="1" r:id="rId3"/>
+    <sheet name="namamani" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -179,39 +179,6 @@
   </si>
   <si>
     <t xml:space="preserve">end</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">这是什么地方？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于失败作</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你身上带着很珍奇的机械呢。让我稍微看一下。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…果然啊。电路设计得太草率了。信号有延迟，电流会波动，时钟齿轮的同步精度也不行，无论哪样都设计得勉勉强强。这样一来根本无法发挥整个运算机构哪怕一半的潜力。
-导力管的布局有太多多余的地方，也没有抗干扰的符刻。如果重组地线的话，应该可以减轻干扰… 嗯，控制符的写法应该也有优化的空间。如果能实现记忆齿轮的动态管理，应该就能大大提高处理效率。
-…我不讨厌这种粗糙的机构。你带了内存芯片吗？ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">给予内存芯片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">下次再说</t>
-  </si>
-  <si>
-    <t xml:space="preserve">失败作？ 那只是无能技师的借口罢了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…好了，这样就没问题了。
-齿轮之间发出赞美一样的鸣响。这正是机械完美运作的律动。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对了，从这家伙身上取下来的旧零件就送给你吧。就当留个纪念。</t>
   </si>
 </sst>
 </file>
@@ -232,19 +199,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -270,7 +237,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -279,54 +246,54 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -340,13 +307,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -522,26 +489,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,24 +546,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -605,11 +572,8 @@
       <c r="K8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" ht="12.8">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
@@ -617,14 +581,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="4" t="s">
@@ -633,26 +597,23 @@
       <c r="K10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
@@ -660,8 +621,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
-      <c r="I24" s="1">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -670,12 +631,9 @@
       <c r="K24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" ht="137.3">
-      <c r="I25" s="1">
+    </row>
+    <row r="25" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -684,11 +642,8 @@
       <c r="K25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" ht="12.8">
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
         <v>30</v>
       </c>
@@ -698,7 +653,7 @@
       <c r="E26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -707,18 +662,15 @@
       <c r="K26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" ht="12.8">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -727,11 +679,8 @@
       <c r="K27" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" ht="12.8">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
@@ -739,13 +688,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
-      <c r="I32" s="1">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -754,21 +703,18 @@
       <c r="K32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" ht="12.8">
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="1" t="s">
         <v>38</v>
       </c>
@@ -776,7 +722,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="1" t="s">
         <v>40</v>
       </c>
@@ -784,7 +730,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="1" t="s">
         <v>42</v>
       </c>
@@ -792,8 +738,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" ht="43.25">
-      <c r="I41" s="1">
+    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J41" s="3" t="s">
@@ -802,26 +748,20 @@
       <c r="K41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="L41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I42" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="L42" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" ht="12.8">
-      <c r="I43" s="1">
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J43" s="1" t="s">
@@ -830,23 +770,20 @@
       <c r="K43" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" ht="12.8">
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E45" s="1" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/namamani.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/namamani.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="namamani" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="namamani" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -179,6 +179,39 @@
   </si>
   <si>
     <t xml:space="preserve">end</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">这是什么地方？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于失败作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你身上带着很珍奇的机械呢。让我稍微看一下。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…果然啊。电路设计得太草率了。信号有延迟，电流会波动，时钟齿轮的同步精度也不行，无论哪样都设计得勉勉强强。这样一来根本无法发挥整个运算机构哪怕一半的潜力。
+导力管的布局有太多多余的地方，也没有抗干扰的符刻。如果重组地线的话，应该可以减轻干扰… 嗯，控制符的写法应该也有优化的空间。如果能实现记忆齿轮的动态管理，应该就能大大提高处理效率。
+…我不讨厌这种粗糙的机构。你带了内存芯片吗？ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">给予内存芯片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下次再说</t>
+  </si>
+  <si>
+    <t xml:space="preserve">失败作？ 那只是无能技师的借口罢了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…好了，这样就没问题了。
+齿轮之间发出赞美一样的鸣响。这正是机械完美运作的律动。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了，从这家伙身上取下来的旧零件就送给你吧。就当留个纪念。</t>
   </si>
 </sst>
 </file>
@@ -199,19 +232,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -237,7 +270,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -246,54 +279,54 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -307,13 +340,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -489,26 +522,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,24 +579,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="12.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -572,8 +605,11 @@
       <c r="K8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
       <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
@@ -581,14 +617,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
       <c r="J10" s="4" t="s">
@@ -597,23 +633,26 @@
       <c r="K10" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="E11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
@@ -621,8 +660,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="1" t="n">
+    <row r="24" ht="12.8">
+      <c r="I24" s="1">
         <v>3</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -631,9 +670,12 @@
       <c r="K24" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="1" t="n">
+      <c r="L24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" ht="137.3">
+      <c r="I25" s="1">
         <v>4</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -642,8 +684,11 @@
       <c r="K25" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" ht="12.8">
       <c r="B26" s="1" t="s">
         <v>30</v>
       </c>
@@ -653,7 +698,7 @@
       <c r="E26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="1" t="n">
+      <c r="I26" s="1">
         <v>5</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -662,15 +707,18 @@
       <c r="K26" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="I27" s="1">
         <v>6</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -679,8 +727,11 @@
       <c r="K27" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
       <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
@@ -688,13 +739,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.8">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="1" t="n">
+    <row r="32" ht="12.8">
+      <c r="I32" s="1">
         <v>7</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -703,18 +754,21 @@
       <c r="K32" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="B33" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="E38" s="1" t="s">
         <v>38</v>
       </c>
@@ -722,7 +776,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="E39" s="1" t="s">
         <v>40</v>
       </c>
@@ -730,7 +784,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="E40" s="1" t="s">
         <v>42</v>
       </c>
@@ -738,8 +792,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I41" s="1" t="n">
+    <row r="41" ht="43.25">
+      <c r="I41" s="1">
         <v>8</v>
       </c>
       <c r="J41" s="3" t="s">
@@ -748,20 +802,26 @@
       <c r="K41" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="E42" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I42" s="1" t="n">
+      <c r="I42" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I43" s="1" t="n">
+      <c r="L42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" ht="12.8">
+      <c r="I43" s="1">
         <v>10</v>
       </c>
       <c r="J43" s="1" t="s">
@@ -770,20 +830,23 @@
       <c r="K43" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" ht="12.8">
       <c r="E45" s="1" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
